--- a/Luban/Excel/GameConfig.xlsx
+++ b/Luban/Excel/GameConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="GameConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>数据参数</t>
   </si>
@@ -105,6 +105,57 @@
   </si>
   <si>
     <t>友方魂体初始炁</t>
+  </si>
+  <si>
+    <t>TraveiIncident1</t>
+  </si>
+  <si>
+    <t>县内移动事件点1（自旅）</t>
+  </si>
+  <si>
+    <t>TraveiIncident2</t>
+  </si>
+  <si>
+    <t>县内移动事件点2（自旅）</t>
+  </si>
+  <si>
+    <t>TraveiIncident3</t>
+  </si>
+  <si>
+    <t>县内移动事件点3（自旅）</t>
+  </si>
+  <si>
+    <t>TraveiIncident4</t>
+  </si>
+  <si>
+    <t>县内移动事件点1（专道）</t>
+  </si>
+  <si>
+    <t>TraveiIncident5</t>
+  </si>
+  <si>
+    <t>县内移动事件点2（专道）</t>
+  </si>
+  <si>
+    <t>TraveiIncidentProbability1</t>
+  </si>
+  <si>
+    <t>县内移动事件触发概率（自旅）</t>
+  </si>
+  <si>
+    <t>TraveiIncidentProbability2</t>
+  </si>
+  <si>
+    <t>县内移动事件触发概率（专道）</t>
+  </si>
+  <si>
+    <t>袭击类旅行事件权重修正（专道）</t>
+  </si>
+  <si>
+    <t>袭击类旅行事件权重修正（精力差）</t>
+  </si>
+  <si>
+    <t>袭击类旅行事件权重修正（精力空）</t>
   </si>
 </sst>
 </file>
@@ -117,7 +168,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,14 +178,20 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A2F45"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -618,137 +675,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -766,6 +823,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1086,8 +1146,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="8.62962962962963" defaultRowHeight="15" outlineLevelCol="2"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultColWidth="8.62962962962963" defaultRowHeight="15.6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.6666666666667" style="2" customWidth="1"/>
     <col min="2" max="2" width="19" style="3" customWidth="1"/>
@@ -1095,12 +1155,12 @@
     <col min="4" max="16384" width="8.62962962962963" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15.6" spans="2:2">
+    <row r="1" s="1" customFormat="1" ht="16.2" spans="2:2">
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15.6" spans="1:3">
+    <row r="2" s="1" customFormat="1" ht="16.2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1111,7 +1171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15.6" spans="1:2">
+    <row r="3" s="1" customFormat="1" ht="16.2" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1249,6 +1309,107 @@
       </c>
       <c r="C18" s="2" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="3">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="3">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="3">
+        <v>4</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="3">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>75</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3">
+        <v>75</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" s="3">
+        <v>-50</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" s="3">
+        <v>50</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" s="3">
+        <v>100</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
